--- a/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_1769_YonoPak.xlsx
+++ b/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_1769_YonoPak.xlsx
@@ -11,7 +11,7 @@
     <sheet name="10月明細" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">10月明細!$A$10:$M$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">10月明細!$A$10:$M$19</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <r>
       <rPr>
@@ -506,6 +506,52 @@
   </si>
   <si>
     <t xml:space="preserve">Yuki Takaoka</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">契約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目のため平準（毎月お支払い）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライダー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1006,7 +1052,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1050,15 +1096,15 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <f aca="false">SUM(L11:L18)</f>
+        <f aca="false">SUM(L11:L19)</f>
         <v>5297.25</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">COUNTA(B11:B18)</f>
-        <v>8</v>
+        <f aca="false">COUNTA(B11:B19)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1415,7 +1461,9 @@
         <f aca="false">I17*K17</f>
         <v>8.5</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="17" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
@@ -1455,10 +1503,54 @@
         <f aca="false">I18*K18</f>
         <v>8.75</v>
       </c>
-      <c r="M18" s="16"/>
+      <c r="M18" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <f aca="false">I19*K19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A10:M18"/>
+  <autoFilter ref="A10:M19"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
